--- a/data/feature-engineering--raw_orders.xlsx
+++ b/data/feature-engineering--raw_orders.xlsx
@@ -14410,7 +14410,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>The raw table has 5 columns; a good feature set expands it to a dozen or more.</t>
+          <t>The raw table has 5 columns; the notebook's feature set expands it to ten.</t>
         </is>
       </c>
     </row>
